--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R67026c17f568424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R4e700978918f4691"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -544,27 +544,11 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="22" t="str">
+      <x:c r="A17" s="24" t="str">
         <x:v>完成条件</x:v>
       </x:c>
-      <x:c r="B17" s="23" t="str">
+      <x:c r="B17" s="25" t="str">
         <x:v>npm run process:hls返回0，五个目标路径可读，四份报告以asset_id和profile闭合</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="22" t="str">
-        <x:v>可验证点</x:v>
-      </x:c>
-      <x:c r="B18" s="23" t="str">
-        <x:v>master引用、profile映射、片段配对、缺片、时长、编码、码率范围、梯度、主原因、动作、来源路径和排序</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="33" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B19" s="25" t="str">
-        <x:v>函数拆分、变量名、注释、内部对象、临时数组、CSV必要引号及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R4e700978918f4691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Re5bc2f97207c4f1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -452,15 +452,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="23" t="str">
-        <x:v>脱敏短视频发布班次中的资产清单、HLS播放列表和放行策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+        <x:v>本次短视频发布班次的资产清单、HLS播放列表和放行策略，资产标识已经脱敏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="22" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
-        <x:v>解压输入数据包后在input_data目录读取data、rules、playlists和starter</x:v>
+        <x:v>在发布前找出播放列表缺片、时长、编码和码率问题，为发布值班提供放行裁决，并把重投指令交给转码平台</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
@@ -481,10 +481,10 @@
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="22" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="23" t="str">
-        <x:v>读取发布清单与策略；解析master；读取variant；检查片段与时长；核对编码和码率；裁决主原因；生成放行与重投报告</x:v>
+        <x:v>用Node.js读取发布清单与策略，解析master和variant播放列表，检查片段、时长、编码和码率，再裁决主原因并生成放行与重投报告</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -537,18 +537,18 @@
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="22" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
-        <x:v>正式处理只读取本地材料，不修改发布清单、策略或播放列表，不连接外部服务</x:v>
+        <x:v>只读取随包发布清单、策略和播放列表，不修改输入文件，也不连接外部服务</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="24" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B17" s="25" t="str">
-        <x:v>npm run process:hls返回0，五个目标路径可读，四份报告以asset_id和profile闭合</x:v>
+        <x:v>交付完成版程序和四份CSV，资产矩阵、variant明细、重投指令与码率梯度以asset_id和profile闭合</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
